--- a/Mediciones/Exploracion/T/RUN_4_5M_T_6NO.xlsx
+++ b/Mediciones/Exploracion/T/RUN_4_5M_T_6NO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Henry\Desktop\Exploracion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GiHub\Resultados_Doc\Mediciones\Exploracion\T\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC04D3EC-0926-4AAA-9D5A-0E8D6DE4FCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B72407-2DA9-4428-A699-2EF90A944BE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -77,9 +77,6 @@
     <t>2026-07-17T15:53:58</t>
   </si>
   <si>
-    <t>Centro de gravedad</t>
-  </si>
-  <si>
     <t>2026-07-17T15:54:03</t>
   </si>
   <si>
@@ -594,6 +591,9 @@
   </si>
   <si>
     <t>}</t>
+  </si>
+  <si>
+    <t>Exploracion frontera</t>
   </si>
 </sst>
 </file>
@@ -946,87 +946,87 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
@@ -1056,397 +1056,397 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D2">
         <v>1.376358692543051E-2</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D3">
         <v>1.376358692543051E-2</v>
@@ -1602,13 +1602,13 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D4">
         <v>1.499461553788763E-2</v>
@@ -1643,13 +1643,13 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D5">
         <v>1.499461553788763E-2</v>
@@ -1684,13 +1684,13 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D6">
         <v>1.499461553788763E-2</v>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D7">
         <v>1.499461553788763E-2</v>
@@ -1766,13 +1766,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D8">
         <v>1.499461553788763E-2</v>
@@ -1807,13 +1807,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D9">
         <v>1.499461553788763E-2</v>
@@ -1848,13 +1848,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D10">
         <v>1.499461553788763E-2</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D11">
         <v>1.499461553788763E-2</v>
@@ -1930,13 +1930,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D12">
         <v>1.499461553788763E-2</v>
@@ -1971,13 +1971,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13">
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D13">
         <v>1.5014583081102069E-2</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D14">
         <v>1.5014583081102069E-2</v>
@@ -2053,13 +2053,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D15">
         <v>1.5014583081102069E-2</v>
@@ -2094,13 +2094,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16">
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D16">
         <v>1.5014583081102069E-2</v>
@@ -2135,13 +2135,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D17">
         <v>1.5014583081102069E-2</v>
@@ -2176,13 +2176,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18">
         <v>16</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D18">
         <v>1.5014583081102069E-2</v>
@@ -2217,13 +2217,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19">
         <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D19">
         <v>1.5014583081102069E-2</v>
@@ -2258,13 +2258,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D20">
         <v>1.5014583081102069E-2</v>
@@ -2299,13 +2299,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D21">
         <v>1.6603090875817419E-2</v>
@@ -2340,13 +2340,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D22">
         <v>1.6603090875817419E-2</v>
@@ -2381,13 +2381,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B23">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D23">
         <v>1.6603090875817419E-2</v>
@@ -2422,13 +2422,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D24">
         <v>1.6603090875817419E-2</v>
@@ -2463,13 +2463,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
         <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D25">
         <v>1.6603090875817419E-2</v>
@@ -2504,13 +2504,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D26">
         <v>1.6603090875817419E-2</v>
@@ -2545,13 +2545,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B27">
         <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D27">
         <v>1.6603090875817419E-2</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28">
         <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D28">
         <v>1.6603090875817419E-2</v>
@@ -2627,13 +2627,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B29">
         <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D29">
         <v>1.6603090875817419E-2</v>
@@ -2668,13 +2668,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30">
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D30">
         <v>1.6603090875817419E-2</v>
@@ -2709,13 +2709,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B31">
         <v>29</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D31">
         <v>1.6603090875817419E-2</v>
@@ -2750,13 +2750,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B32">
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D32">
         <v>1.6603090875817419E-2</v>
@@ -2791,13 +2791,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33">
         <v>31</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D33">
         <v>1.6603090875817419E-2</v>
@@ -2832,13 +2832,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34">
         <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D34">
         <v>1.7671570180913691E-2</v>
@@ -2873,13 +2873,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D35">
         <v>1.7671570180913691E-2</v>
@@ -2914,13 +2914,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36">
         <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D36">
         <v>1.776521504926569E-2</v>
@@ -2955,13 +2955,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B37">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D37">
         <v>1.776521504926569E-2</v>
@@ -2996,13 +2996,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38">
         <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D38">
         <v>1.776521504926569E-2</v>
@@ -3037,13 +3037,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39">
         <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D39">
         <v>1.776521504926569E-2</v>
@@ -3078,13 +3078,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B40">
         <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D40">
         <v>1.776521504926569E-2</v>
@@ -3119,13 +3119,13 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B41">
         <v>39</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D41">
         <v>1.776521504926569E-2</v>
@@ -3160,13 +3160,13 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B42">
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D42">
         <v>1.776521504926569E-2</v>
@@ -3201,13 +3201,13 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B43">
         <v>41</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D43">
         <v>1.776521504926569E-2</v>
@@ -3242,13 +3242,13 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B44">
         <v>42</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D44">
         <v>1.776521504926569E-2</v>
@@ -3283,13 +3283,13 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B45">
         <v>43</v>
       </c>
       <c r="C45" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D45">
         <v>1.776521504926569E-2</v>
@@ -3324,13 +3324,13 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B46">
         <v>44</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D46">
         <v>1.776521504926569E-2</v>
@@ -3365,13 +3365,13 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B47">
         <v>45</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D47">
         <v>1.776521504926569E-2</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B48">
         <v>46</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D48">
         <v>1.776521504926569E-2</v>
@@ -3447,13 +3447,13 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B49">
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D49">
         <v>1.776521504926569E-2</v>
@@ -3488,13 +3488,13 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50">
         <v>48</v>
       </c>
       <c r="C50" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D50">
         <v>1.776521504926569E-2</v>
@@ -3529,13 +3529,13 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B51">
         <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D51">
         <v>1.776521504926569E-2</v>
@@ -3570,13 +3570,13 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B52">
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D52">
         <v>1.776521504926569E-2</v>
@@ -3611,13 +3611,13 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B53">
         <v>51</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D53">
         <v>1.776521504926569E-2</v>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B54">
         <v>52</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D54">
         <v>1.776521504926569E-2</v>
@@ -3693,13 +3693,13 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B55">
         <v>53</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D55">
         <v>1.776521504926569E-2</v>
@@ -3734,13 +3734,13 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56">
         <v>54</v>
       </c>
       <c r="C56" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D56">
         <v>1.776521504926569E-2</v>
@@ -3775,13 +3775,13 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57">
         <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D57">
         <v>1.776521504926569E-2</v>
@@ -3816,13 +3816,13 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58">
         <v>56</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D58">
         <v>1.776521504926569E-2</v>
@@ -3857,13 +3857,13 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59">
         <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D59">
         <v>1.776521504926569E-2</v>
@@ -3898,13 +3898,13 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B60">
         <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D60">
         <v>1.776521504926569E-2</v>
@@ -3939,13 +3939,13 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61">
         <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D61">
         <v>1.776521504926569E-2</v>
@@ -3980,13 +3980,13 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62">
         <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D62">
         <v>2.0805254816155069E-2</v>
@@ -4021,13 +4021,13 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63">
         <v>61</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D63">
         <v>2.0805254816155069E-2</v>
@@ -4062,13 +4062,13 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B64">
         <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D64">
         <v>2.159208826644279E-2</v>
@@ -4103,13 +4103,13 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B65">
         <v>63</v>
       </c>
       <c r="C65" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D65">
         <v>2.4967398616918341E-2</v>
@@ -4144,13 +4144,13 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66">
         <v>64</v>
       </c>
       <c r="C66" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D66">
         <v>3.4086959956632627E-2</v>
@@ -4185,13 +4185,13 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67">
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D67">
         <v>0.2420008469514757</v>
@@ -4226,13 +4226,13 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B68">
         <v>66</v>
       </c>
       <c r="C68" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D68">
         <v>0.70832250676581421</v>
@@ -4267,13 +4267,13 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B69">
         <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D69">
         <v>0.97587703675165205</v>
@@ -4308,13 +4308,13 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B70">
         <v>68</v>
       </c>
       <c r="C70" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D70">
         <v>0.97587703675165205</v>
@@ -4349,13 +4349,13 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B71">
         <v>69</v>
       </c>
       <c r="C71" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D71">
         <v>0.97587703675165205</v>
@@ -4390,13 +4390,13 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B72">
         <v>70</v>
       </c>
       <c r="C72" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D72">
         <v>0.97587703675165205</v>
@@ -4431,13 +4431,13 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B73">
         <v>71</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D73">
         <v>0.97587703675165205</v>
@@ -4472,13 +4472,13 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B74">
         <v>72</v>
       </c>
       <c r="C74" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D74">
         <v>0.97587703675165205</v>
@@ -4513,13 +4513,13 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B75">
         <v>73</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D75">
         <v>0.97587703675165205</v>
@@ -4554,13 +4554,13 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B76">
         <v>74</v>
       </c>
       <c r="C76" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D76">
         <v>0.97587703675165205</v>
@@ -4595,13 +4595,13 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B77">
         <v>75</v>
       </c>
       <c r="C77" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D77">
         <v>0.97587703675165205</v>
@@ -4636,13 +4636,13 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B78">
         <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D78">
         <v>0.97587703675165205</v>
@@ -4677,13 +4677,13 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B79">
         <v>77</v>
       </c>
       <c r="C79" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D79">
         <v>0.97587703675165205</v>
@@ -4718,13 +4718,13 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B80">
         <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D80">
         <v>0.97587703675165205</v>
@@ -4759,13 +4759,13 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B81">
         <v>79</v>
       </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D81">
         <v>0.97587703675165205</v>
@@ -4800,13 +4800,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82">
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D82">
         <v>0.97587703675165205</v>
@@ -4841,13 +4841,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83">
         <v>81</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D83">
         <v>0.97587703675165205</v>
@@ -4882,13 +4882,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B84">
         <v>82</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D84">
         <v>0.97587703675165205</v>
@@ -4923,13 +4923,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B85">
         <v>83</v>
       </c>
       <c r="C85" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D85">
         <v>0.97587703675165205</v>
@@ -4964,13 +4964,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B86">
         <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D86">
         <v>0.97587703675165205</v>
@@ -5005,13 +5005,13 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B87">
         <v>85</v>
       </c>
       <c r="C87" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D87">
         <v>0.97587703675165205</v>
@@ -5046,13 +5046,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B88">
         <v>86</v>
       </c>
       <c r="C88" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D88">
         <v>0.97587703675165205</v>
@@ -5087,13 +5087,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B89">
         <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D89">
         <v>0.97587703675165205</v>
@@ -5128,13 +5128,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B90">
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D90">
         <v>0.97587703675165205</v>
@@ -5169,13 +5169,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B91">
         <v>89</v>
       </c>
       <c r="C91" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D91">
         <v>0.97587703675165205</v>
@@ -5210,13 +5210,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B92">
         <v>90</v>
       </c>
       <c r="C92" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D92">
         <v>0.97587703675165205</v>
@@ -5251,13 +5251,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B93">
         <v>91</v>
       </c>
       <c r="C93" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D93">
         <v>0.97587703675165205</v>
@@ -5292,13 +5292,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B94">
         <v>92</v>
       </c>
       <c r="C94" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D94">
         <v>0.97587703675165205</v>
@@ -5333,13 +5333,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B95">
         <v>93</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D95">
         <v>0.97587703675165205</v>
@@ -5374,13 +5374,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B96">
         <v>94</v>
       </c>
       <c r="C96" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D96">
         <v>0.97587703675165205</v>
@@ -5415,13 +5415,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B97">
         <v>95</v>
       </c>
       <c r="C97" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D97">
         <v>0.97587703675165205</v>
@@ -5456,13 +5456,13 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B98">
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D98">
         <v>0.97587703675165205</v>
@@ -5497,13 +5497,13 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B99">
         <v>97</v>
       </c>
       <c r="C99" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D99">
         <v>0.97587703675165205</v>
@@ -5538,13 +5538,13 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B100">
         <v>98</v>
       </c>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D100">
         <v>0.97587703675165205</v>
@@ -5579,13 +5579,13 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B101">
         <v>99</v>
       </c>
       <c r="C101" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D101">
         <v>0.97587703675165205</v>
@@ -5620,13 +5620,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B102">
         <v>100</v>
       </c>
       <c r="C102" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D102">
         <v>0.97587703675165205</v>
@@ -5661,13 +5661,13 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B103">
         <v>101</v>
       </c>
       <c r="C103" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D103">
         <v>0.97587703675165205</v>
@@ -5702,13 +5702,13 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B104">
         <v>102</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D104">
         <v>0.97587703675165205</v>
@@ -5743,13 +5743,13 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B105">
         <v>103</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D105">
         <v>0.97587703675165205</v>
@@ -5784,13 +5784,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B106">
         <v>104</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D106">
         <v>0.97587703675165205</v>
@@ -5825,13 +5825,13 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B107">
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D107">
         <v>0.97587703675165205</v>
@@ -5866,13 +5866,13 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B108">
         <v>106</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D108">
         <v>0.97587703675165205</v>
@@ -5907,13 +5907,13 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B109">
         <v>107</v>
       </c>
       <c r="C109" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D109">
         <v>0.97587703675165205</v>
@@ -5948,13 +5948,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B110">
         <v>108</v>
       </c>
       <c r="C110" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D110">
         <v>0.97587703675165205</v>
@@ -5989,13 +5989,13 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B111">
         <v>109</v>
       </c>
       <c r="C111" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D111">
         <v>0.97587703675165205</v>
@@ -6030,13 +6030,13 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B112">
         <v>110</v>
       </c>
       <c r="C112" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D112">
         <v>0.97587703675165205</v>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B113">
         <v>111</v>
       </c>
       <c r="C113" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D113">
         <v>0.97587703675165205</v>
@@ -6112,13 +6112,13 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B114">
         <v>112</v>
       </c>
       <c r="C114" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D114">
         <v>0.97587703675165205</v>
@@ -6153,13 +6153,13 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B115">
         <v>113</v>
       </c>
       <c r="C115" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D115">
         <v>0.97587703675165205</v>
@@ -6194,13 +6194,13 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B116">
         <v>114</v>
       </c>
       <c r="C116" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D116">
         <v>0.97587703675165205</v>
@@ -6235,13 +6235,13 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B117">
         <v>115</v>
       </c>
       <c r="C117" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D117">
         <v>0.97587703675165205</v>
@@ -6276,13 +6276,13 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B118">
         <v>116</v>
       </c>
       <c r="C118" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D118">
         <v>0.97587703675165205</v>
@@ -6317,13 +6317,13 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B119">
         <v>117</v>
       </c>
       <c r="C119" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D119">
         <v>0.97587703675165205</v>
@@ -6358,13 +6358,13 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B120">
         <v>118</v>
       </c>
       <c r="C120" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D120">
         <v>0.97587703675165205</v>
@@ -6399,13 +6399,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B121">
         <v>119</v>
       </c>
       <c r="C121" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
       <c r="D121">
         <v>0.97587703675165205</v>
@@ -6455,25 +6455,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" t="s">
         <v>77</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -8378,10 +8378,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -8441,13 +8441,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -9369,16 +9369,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" t="s">
         <v>85</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>86</v>
-      </c>
-      <c r="D1" t="s">
-        <v>87</v>
       </c>
       <c r="E1" t="s">
         <v>10</v>
@@ -11814,16 +11814,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
         <v>88</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>89</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>90</v>
-      </c>
-      <c r="D1" t="s">
-        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -11842,15 +11842,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" t="s">
         <v>92</v>
-      </c>
-      <c r="B1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -11858,7 +11858,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3">
         <v>1.9</v>
@@ -11866,7 +11866,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -11874,7 +11874,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B5">
         <v>1.2</v>
@@ -11885,12 +11885,12 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B7">
         <v>120</v>
@@ -11922,7 +11922,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11">
         <v>0.97587699999999999</v>
@@ -11930,7 +11930,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12">
         <v>1.501177680003458</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13">
         <v>110.4111327000137</v>
@@ -11946,7 +11946,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B14">
         <v>1.359625287136712E-2</v>
@@ -11954,7 +11954,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -11962,12 +11962,12 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B17">
         <v>0</v>
